--- a/ig/main/ValueSet-jdv-j350-type-act-de-soin-amm-finess.xlsx
+++ b/ig/main/ValueSet-jdv-j350-type-act-de-soin-amm-finess.xlsx
@@ -8,14 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Expansion Parameters" r:id="rId5" sheetId="3"/>
-    <sheet name="Expansion" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -120,36 +118,6 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r392-type-act-smsse-regulee</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>used-codesystem</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r392-type-act-smsse-regulee|20260629120000</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>Inactive</t>
   </si>
 </sst>
 </file>
@@ -461,71 +429,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>40</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>42</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>